--- a/erp-server/erp-server-oms/src/main/resources/excel/SoPriceTemplate.xlsx
+++ b/erp-server/erp-server-oms/src/main/resources/excel/SoPriceTemplate.xlsx
@@ -32,43 +32,7 @@
     <author>Admin</author>
   </authors>
   <commentList>
-    <comment ref="B1" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>不填写默认为今天</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="D1" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>不填写，则默认为东莞市简拍智造科技有限公司</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="H1" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>三位币制代码，如CNY，USD</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="J1" authorId="0">
+    <comment ref="I1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -80,38 +44,20 @@
         </r>
       </text>
     </comment>
-    <comment ref="K1" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>格式yyyy/MM/dd</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="L1" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>请填写启用或者停用</t>
-        </r>
-      </text>
-    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -135,13 +81,43 @@
     </r>
   </si>
   <si>
-    <t>报价日期</t>
+    <r>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>报价日期</t>
+    </r>
   </si>
   <si>
-    <t>定价员</t>
+    <r>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>报价员</t>
+    </r>
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -175,20 +151,7 @@
     </r>
   </si>
   <si>
-    <t>区间从</t>
-  </si>
-  <si>
-    <t>区间到</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
+    <r>
       <t>*</t>
     </r>
     <r>
@@ -199,7 +162,22 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>币制代码</t>
+      <t>区间从</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>区间到</t>
     </r>
   </si>
   <si>
@@ -224,6 +202,20 @@
   </si>
   <si>
     <r>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>税率</t>
+    </r>
+  </si>
+  <si>
+    <r>
       <rPr>
         <sz val="10.5"/>
         <color rgb="FFFF0000"/>
@@ -236,44 +228,26 @@
       <rPr>
         <sz val="10.5"/>
         <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>税率</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>生效时间</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="等线"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>%</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>*</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>生效时间</t>
-    </r>
-  </si>
-  <si>
-    <t>启用状态</t>
+      <t>失效时间</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -286,7 +260,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="29">
+  <fonts count="31">
     <font>
       <sz val="10"/>
       <color theme="1"/>
@@ -302,14 +276,14 @@
     </font>
     <font>
       <sz val="10.5"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
       <color rgb="FF000000"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10.5"/>
-      <color rgb="FFFF0000"/>
       <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -317,6 +291,13 @@
     <font>
       <sz val="9.75"/>
       <color rgb="FF000000"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
       <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -471,6 +452,12 @@
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="10.5"/>
@@ -479,10 +466,11 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="10.5"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
-      <name val="Calibri"/>
+      <name val="等线"/>
       <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="10.5"/>
@@ -800,152 +788,152 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -958,22 +946,25 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1297,18 +1288,17 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:M17"/>
+  <dimension ref="A1:K17"/>
   <sheetFormatPr defaultColWidth="14" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="34.8571428571429" customWidth="1"/>
     <col min="2" max="3" width="20" customWidth="1"/>
     <col min="4" max="4" width="27.2857142857143" customWidth="1"/>
     <col min="5" max="5" width="31.7142857142857" style="1" customWidth="1"/>
-    <col min="6" max="11" width="20" customWidth="1"/>
-    <col min="12" max="12" width="20" style="1" customWidth="1"/>
+    <col min="6" max="10" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.25" spans="1:13">
+    <row r="1" ht="14.25" spans="1:11">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1330,231 +1320,199 @@
       <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
       <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="5" t="s">
+      <c r="K1" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="8"/>
-    </row>
-    <row r="2" ht="13.5" spans="1:13">
-      <c r="A2" s="3"/>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
+    </row>
+    <row r="2" ht="13.5" spans="1:11">
+      <c r="A2" s="5"/>
+      <c r="B2" s="5"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
       <c r="E2" s="6"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
-      <c r="I2" s="3"/>
-      <c r="J2" s="3"/>
-      <c r="K2" s="3"/>
-      <c r="L2" s="6"/>
-      <c r="M2" s="8"/>
-    </row>
-    <row r="3" ht="13.5" spans="1:13">
-      <c r="A3" s="3"/>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
+      <c r="F2" s="5"/>
+      <c r="G2" s="5"/>
+      <c r="H2" s="5"/>
+      <c r="I2" s="5"/>
+      <c r="J2" s="5"/>
+      <c r="K2" s="8"/>
+    </row>
+    <row r="3" ht="13.5" spans="1:11">
+      <c r="A3" s="5"/>
+      <c r="B3" s="5"/>
+      <c r="C3" s="5"/>
+      <c r="D3" s="5"/>
       <c r="E3" s="6"/>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3"/>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3"/>
-      <c r="J3" s="3"/>
-      <c r="K3" s="3"/>
-      <c r="L3" s="6"/>
-      <c r="M3" s="8"/>
-    </row>
-    <row r="4" ht="13.5" spans="1:13">
-      <c r="A4" s="3"/>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
+      <c r="F3" s="5"/>
+      <c r="G3" s="5"/>
+      <c r="H3" s="5"/>
+      <c r="I3" s="5"/>
+      <c r="J3" s="5"/>
+      <c r="K3" s="8"/>
+    </row>
+    <row r="4" ht="13.5" spans="1:11">
+      <c r="A4" s="5"/>
+      <c r="B4" s="5"/>
+      <c r="C4" s="5"/>
+      <c r="D4" s="5"/>
       <c r="E4" s="6"/>
-      <c r="F4" s="3"/>
-      <c r="G4" s="3"/>
-      <c r="H4" s="3"/>
-      <c r="I4" s="3"/>
-      <c r="J4" s="3"/>
-      <c r="K4" s="3"/>
-      <c r="L4" s="6"/>
-      <c r="M4" s="8"/>
-    </row>
-    <row r="5" ht="13.5" spans="2:13">
-      <c r="B5" s="3"/>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
+      <c r="F4" s="5"/>
+      <c r="G4" s="5"/>
+      <c r="H4" s="5"/>
+      <c r="I4" s="5"/>
+      <c r="J4" s="5"/>
+      <c r="K4" s="8"/>
+    </row>
+    <row r="5" ht="13.5" spans="2:11">
+      <c r="B5" s="5"/>
+      <c r="C5" s="5"/>
+      <c r="D5" s="5"/>
       <c r="E5" s="6"/>
-      <c r="F5" s="3"/>
-      <c r="G5" s="3"/>
-      <c r="H5" s="3"/>
-      <c r="I5" s="3"/>
-      <c r="J5" s="3"/>
-      <c r="K5" s="3"/>
-      <c r="L5" s="6"/>
-      <c r="M5" s="8"/>
-    </row>
-    <row r="6" ht="13.5" spans="2:13">
-      <c r="B6" s="3"/>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
+      <c r="F5" s="5"/>
+      <c r="G5" s="5"/>
+      <c r="H5" s="5"/>
+      <c r="I5" s="5"/>
+      <c r="J5" s="5"/>
+      <c r="K5" s="8"/>
+    </row>
+    <row r="6" ht="13.5" spans="2:11">
+      <c r="B6" s="5"/>
+      <c r="C6" s="5"/>
+      <c r="D6" s="5"/>
       <c r="E6" s="6"/>
-      <c r="F6" s="3"/>
-      <c r="G6" s="3"/>
-      <c r="H6" s="3"/>
-      <c r="I6" s="3"/>
-      <c r="J6" s="3"/>
-      <c r="K6" s="3"/>
-      <c r="L6" s="6"/>
-      <c r="M6" s="8"/>
-    </row>
-    <row r="7" ht="13.5" spans="2:13">
-      <c r="B7" s="3"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
+      <c r="F6" s="5"/>
+      <c r="G6" s="5"/>
+      <c r="H6" s="5"/>
+      <c r="I6" s="5"/>
+      <c r="J6" s="5"/>
+      <c r="K6" s="8"/>
+    </row>
+    <row r="7" ht="13.5" spans="2:11">
+      <c r="B7" s="5"/>
+      <c r="C7" s="5"/>
+      <c r="D7" s="5"/>
       <c r="E7" s="6"/>
-      <c r="F7" s="3"/>
-      <c r="G7" s="3"/>
-      <c r="H7" s="3"/>
-      <c r="I7" s="3"/>
-      <c r="J7" s="3"/>
-      <c r="K7" s="3"/>
-      <c r="L7" s="6"/>
-      <c r="M7" s="8"/>
-    </row>
-    <row r="8" ht="13.5" spans="1:13">
+      <c r="F7" s="5"/>
+      <c r="G7" s="5"/>
+      <c r="H7" s="5"/>
+      <c r="I7" s="5"/>
+      <c r="J7" s="5"/>
+      <c r="K7" s="8"/>
+    </row>
+    <row r="8" ht="13.5" spans="1:11">
       <c r="A8" s="7"/>
-      <c r="B8" s="3"/>
-      <c r="C8" s="3"/>
-      <c r="D8" s="3"/>
+      <c r="B8" s="5"/>
+      <c r="C8" s="5"/>
+      <c r="D8" s="5"/>
       <c r="E8" s="6"/>
-      <c r="F8" s="3"/>
-      <c r="G8" s="3"/>
-      <c r="H8" s="3"/>
-      <c r="I8" s="3"/>
-      <c r="J8" s="3"/>
-      <c r="K8" s="3"/>
-      <c r="L8" s="6"/>
-      <c r="M8" s="8"/>
-    </row>
-    <row r="9" ht="13.5" spans="1:13">
+      <c r="F8" s="5"/>
+      <c r="G8" s="5"/>
+      <c r="H8" s="5"/>
+      <c r="I8" s="5"/>
+      <c r="J8" s="5"/>
+      <c r="K8" s="8"/>
+    </row>
+    <row r="9" ht="13.5" spans="1:11">
       <c r="A9" s="7"/>
-      <c r="B9" s="3"/>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
+      <c r="B9" s="5"/>
+      <c r="C9" s="5"/>
+      <c r="D9" s="5"/>
       <c r="E9" s="6"/>
-      <c r="F9" s="3"/>
-      <c r="G9" s="3"/>
-      <c r="H9" s="3"/>
-      <c r="I9" s="3"/>
-      <c r="J9" s="3"/>
-      <c r="K9" s="3"/>
-      <c r="L9" s="6"/>
-      <c r="M9" s="8"/>
-    </row>
-    <row r="10" ht="13.5" spans="1:13">
+      <c r="F9" s="5"/>
+      <c r="G9" s="5"/>
+      <c r="H9" s="5"/>
+      <c r="I9" s="5"/>
+      <c r="J9" s="5"/>
+      <c r="K9" s="8"/>
+    </row>
+    <row r="10" ht="13.5" spans="1:11">
       <c r="A10" s="7"/>
-      <c r="B10" s="3"/>
-      <c r="C10" s="3"/>
-      <c r="D10" s="3"/>
+      <c r="B10" s="5"/>
+      <c r="C10" s="5"/>
+      <c r="D10" s="5"/>
       <c r="E10" s="6"/>
-      <c r="F10" s="3"/>
-      <c r="G10" s="3"/>
-      <c r="H10" s="3"/>
-      <c r="I10" s="3"/>
-      <c r="J10" s="3"/>
-      <c r="K10" s="3"/>
-      <c r="L10" s="6"/>
-      <c r="M10" s="8"/>
-    </row>
-    <row r="11" ht="13.5" spans="1:13">
+      <c r="F10" s="5"/>
+      <c r="G10" s="5"/>
+      <c r="H10" s="5"/>
+      <c r="I10" s="5"/>
+      <c r="J10" s="5"/>
+      <c r="K10" s="8"/>
+    </row>
+    <row r="11" ht="13.5" spans="1:11">
       <c r="A11" s="7"/>
-      <c r="B11" s="3"/>
-      <c r="C11" s="3"/>
-      <c r="D11" s="3"/>
+      <c r="B11" s="5"/>
+      <c r="C11" s="5"/>
+      <c r="D11" s="5"/>
       <c r="E11" s="6"/>
-      <c r="F11" s="3"/>
-      <c r="G11" s="3"/>
-      <c r="H11" s="3"/>
-      <c r="I11" s="3"/>
-      <c r="J11" s="3"/>
-      <c r="K11" s="3"/>
-      <c r="L11" s="6"/>
-      <c r="M11" s="8"/>
-    </row>
-    <row r="12" ht="13.5" spans="1:13">
+      <c r="F11" s="5"/>
+      <c r="G11" s="5"/>
+      <c r="H11" s="5"/>
+      <c r="I11" s="5"/>
+      <c r="J11" s="5"/>
+      <c r="K11" s="8"/>
+    </row>
+    <row r="12" ht="13.5" spans="1:11">
       <c r="A12" s="7"/>
-      <c r="B12" s="3"/>
-      <c r="C12" s="3"/>
-      <c r="D12" s="3"/>
+      <c r="B12" s="5"/>
+      <c r="C12" s="5"/>
+      <c r="D12" s="5"/>
       <c r="E12" s="6"/>
-      <c r="F12" s="3"/>
-      <c r="G12" s="3"/>
-      <c r="H12" s="3"/>
-      <c r="I12" s="3"/>
-      <c r="J12" s="3"/>
-      <c r="K12" s="3"/>
-      <c r="L12" s="6"/>
-      <c r="M12" s="8"/>
-    </row>
-    <row r="13" ht="13.5" spans="1:13">
-      <c r="A13" s="3"/>
-      <c r="B13" s="3"/>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
+      <c r="F12" s="5"/>
+      <c r="G12" s="5"/>
+      <c r="H12" s="5"/>
+      <c r="I12" s="5"/>
+      <c r="J12" s="5"/>
+      <c r="K12" s="8"/>
+    </row>
+    <row r="13" ht="13.5" spans="1:11">
+      <c r="A13" s="5"/>
+      <c r="B13" s="5"/>
+      <c r="C13" s="5"/>
+      <c r="D13" s="5"/>
       <c r="E13" s="6"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="3"/>
-      <c r="H13" s="3"/>
-      <c r="I13" s="3"/>
-      <c r="J13" s="3"/>
-      <c r="K13" s="3"/>
-      <c r="L13" s="6"/>
-      <c r="M13" s="8"/>
-    </row>
-    <row r="14" ht="13.5" spans="1:13">
-      <c r="A14" s="3"/>
-      <c r="B14" s="3"/>
-      <c r="C14" s="3"/>
-      <c r="D14" s="3"/>
+      <c r="F13" s="5"/>
+      <c r="G13" s="5"/>
+      <c r="H13" s="5"/>
+      <c r="I13" s="5"/>
+      <c r="J13" s="5"/>
+      <c r="K13" s="8"/>
+    </row>
+    <row r="14" ht="13.5" spans="1:11">
+      <c r="A14" s="5"/>
+      <c r="B14" s="5"/>
+      <c r="C14" s="5"/>
+      <c r="D14" s="5"/>
       <c r="E14" s="6"/>
-      <c r="F14" s="3"/>
-      <c r="G14" s="3"/>
-      <c r="H14" s="3"/>
-      <c r="I14" s="3"/>
-      <c r="J14" s="3"/>
-      <c r="K14" s="3"/>
-      <c r="L14" s="6"/>
-      <c r="M14" s="8"/>
-    </row>
-    <row r="15" ht="13.5" spans="1:13">
-      <c r="A15" s="3"/>
-      <c r="B15" s="3"/>
-      <c r="C15" s="3"/>
-      <c r="D15" s="3"/>
+      <c r="F14" s="5"/>
+      <c r="G14" s="5"/>
+      <c r="H14" s="5"/>
+      <c r="I14" s="5"/>
+      <c r="J14" s="5"/>
+      <c r="K14" s="8"/>
+    </row>
+    <row r="15" ht="13.5" spans="1:11">
+      <c r="A15" s="5"/>
+      <c r="B15" s="5"/>
+      <c r="C15" s="5"/>
+      <c r="D15" s="5"/>
       <c r="E15" s="6"/>
-      <c r="F15" s="3"/>
-      <c r="G15" s="3"/>
-      <c r="H15" s="3"/>
-      <c r="I15" s="3"/>
-      <c r="J15" s="3"/>
-      <c r="K15" s="3"/>
-      <c r="L15" s="6"/>
-      <c r="M15" s="8"/>
-    </row>
-    <row r="16" spans="1:13">
+      <c r="F15" s="5"/>
+      <c r="G15" s="5"/>
+      <c r="H15" s="5"/>
+      <c r="I15" s="5"/>
+      <c r="J15" s="5"/>
+      <c r="K15" s="8"/>
+    </row>
+    <row r="16" spans="1:11">
       <c r="A16" s="8"/>
       <c r="B16" s="8"/>
       <c r="C16" s="8"/>
@@ -1566,10 +1524,8 @@
       <c r="I16" s="8"/>
       <c r="J16" s="8"/>
       <c r="K16" s="8"/>
-      <c r="L16" s="9"/>
-      <c r="M16" s="8"/>
-    </row>
-    <row r="17" spans="1:13">
+    </row>
+    <row r="17" spans="1:11">
       <c r="A17" s="8"/>
       <c r="B17" s="8"/>
       <c r="C17" s="8"/>
@@ -1581,15 +1537,8 @@
       <c r="I17" s="8"/>
       <c r="J17" s="8"/>
       <c r="K17" s="8"/>
-      <c r="L17" s="9"/>
-      <c r="M17" s="8"/>
     </row>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L2:L1048576">
-      <formula1>"启用,停用"</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
   <legacyDrawing r:id="rId2"/>
